--- a/mv-design-pro/frontend/e2e/fixtures/arkusz-siec-sn.xlsx
+++ b/mv-design-pro/frontend/e2e/fixtures/arkusz-siec-sn.xlsx
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,6 +686,11 @@
           <t>zaczep_krok_pct</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tolerancja_nN</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -725,6 +730,11 @@
       </c>
       <c r="J2" t="n">
         <v>2.5</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>PLUS_6</t>
+        </is>
       </c>
     </row>
   </sheetData>
